--- a/site/StructureDefinition-hcen-medication-request.xlsx
+++ b/site/StructureDefinition-hcen-medication-request.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -684,7 +684,7 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t>Código que identifica el medicamento prescripto (SNOMED CT u otra terminología)</t>
+    <t>Código que identifica el medicamento prescripto (SNOMED CT u otra terminología, p.ej. un tesauro clínico institucional)</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
@@ -766,10 +766,10 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
+    <t>Slicing abierto por system: además del slice snomed, admite otra codificación con su propio system — p.ej. un código de un tesauro clínico (ver sección 4.7.4 Tesauro clínico)</t>
+  </si>
+  <si>
+    <t>El slicing es abierto por system. Además del slice snomed, se puede incluir una codificación adicional de otro vocabulario — p.ej. un código de un tesauro clínico (ver [Tesauro clínico](hcen-terminologia.html#tesauro-clínico), sección 4.7.4). La URI de ese system depende de la institución de origen y su confirmación es externa a esta guía; no se fija ni se valida en este perfil.</t>
   </si>
   <si>
     <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
